--- a/artfynd/A 29620-2023 artfynd.xlsx
+++ b/artfynd/A 29620-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29620-2023 artfynd.xlsx
+++ b/artfynd/A 29620-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73274592</v>
+        <v>73274539</v>
       </c>
       <c r="B2" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613992.0456134723</v>
+        <v>614040</v>
       </c>
       <c r="R2" t="n">
-        <v>6990619.049916837</v>
+        <v>6990574</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73274558</v>
+        <v>73274538</v>
       </c>
       <c r="B3" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613677.1657628217</v>
+        <v>613999</v>
       </c>
       <c r="R3" t="n">
-        <v>6991010.978411691</v>
+        <v>6990618</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73274542</v>
+        <v>73274540</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614098.9977805596</v>
+        <v>614060</v>
       </c>
       <c r="R4" t="n">
-        <v>6990514.21765488</v>
+        <v>6990555</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2017-08-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-08-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73274531</v>
+        <v>73274542</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613916.9835380117</v>
+        <v>614099</v>
       </c>
       <c r="R5" t="n">
-        <v>6990696.832184612</v>
+        <v>6990514</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2017-08-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-08-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73274540</v>
+        <v>73274537</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>614059.801780494</v>
+        <v>613992</v>
       </c>
       <c r="R6" t="n">
-        <v>6990555.095116745</v>
+        <v>6990619</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2017-08-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-08-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73274603</v>
+        <v>73274917</v>
       </c>
       <c r="B7" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>102613</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>614040.0326577269</v>
+        <v>614143</v>
       </c>
       <c r="R7" t="n">
-        <v>6990573.937665315</v>
+        <v>6990478</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,22 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-08-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-08-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73274567</v>
+        <v>73274499</v>
       </c>
       <c r="B8" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613900.1423836657</v>
+        <v>613677</v>
       </c>
       <c r="R8" t="n">
-        <v>6990723.046074228</v>
+        <v>6991011</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,22 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>73274593</v>
+        <v>73274529</v>
       </c>
       <c r="B9" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>220093</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>614096.9083155795</v>
+        <v>613902</v>
       </c>
       <c r="R9" t="n">
-        <v>6990495.970935412</v>
+        <v>6990721</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,22 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>73274529</v>
+        <v>73274541</v>
       </c>
       <c r="B10" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220093</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613902.0393672077</v>
+        <v>614097</v>
       </c>
       <c r="R10" t="n">
-        <v>6990720.841022136</v>
+        <v>6990496</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1519,9 @@
           <t>2017-08-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2017-08-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,37 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>73274589</v>
+        <v>73274530</v>
       </c>
       <c r="B11" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613998.9091824414</v>
+        <v>613900</v>
       </c>
       <c r="R11" t="n">
-        <v>6990617.92761736</v>
+        <v>6990723</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,22 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2017-07-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-08-14</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 29620-2023 artfynd.xlsx
+++ b/artfynd/A 29620-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73274539</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73274538</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73274540</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73274542</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73274537</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73274917</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73274499</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73274529</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73274541</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,8 +1692,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73274530</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>